--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/2.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/2.xlsx
@@ -426,13 +426,13 @@
         <v>-18.85147351073381</v>
       </c>
       <c r="E2">
-        <v>-7.664267724203383</v>
+        <v>-5.707849212565589</v>
       </c>
       <c r="F2">
-        <v>1.202227732469768</v>
+        <v>0.8950283775224012</v>
       </c>
       <c r="G2">
-        <v>-15.95628109939594</v>
+        <v>-15.25194267264276</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.43995398685545</v>
       </c>
       <c r="E3">
-        <v>-8.902977447313518</v>
+        <v>-6.990077570889436</v>
       </c>
       <c r="F3">
-        <v>0.8129844925730606</v>
+        <v>0.451522621844992</v>
       </c>
       <c r="G3">
-        <v>-16.29187110071186</v>
+        <v>-14.93685984566985</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.90811425435502</v>
       </c>
       <c r="E4">
-        <v>-8.194429761703374</v>
+        <v>-7.967073195674277</v>
       </c>
       <c r="F4">
-        <v>0.8240625154515595</v>
+        <v>0.6757452890588244</v>
       </c>
       <c r="G4">
-        <v>-15.62865461537473</v>
+        <v>-14.21927592621405</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.33468253150277</v>
       </c>
       <c r="E5">
-        <v>-8.933766542091668</v>
+        <v>-8.405791757537381</v>
       </c>
       <c r="F5">
-        <v>1.3093606865315</v>
+        <v>0.9828670424163347</v>
       </c>
       <c r="G5">
-        <v>-15.15682573348119</v>
+        <v>-15.21052443740093</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.760112581622</v>
       </c>
       <c r="E6">
-        <v>-10.70857060365184</v>
+        <v>-9.85073271543083</v>
       </c>
       <c r="F6">
-        <v>1.201879317168371</v>
+        <v>0.7243286354267603</v>
       </c>
       <c r="G6">
-        <v>-15.23510192748448</v>
+        <v>-13.50165890130285</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.23535989052617</v>
       </c>
       <c r="E7">
-        <v>-10.2899041246947</v>
+        <v>-8.117038140912289</v>
       </c>
       <c r="F7">
-        <v>1.110520074024416</v>
+        <v>1.151178555991493</v>
       </c>
       <c r="G7">
-        <v>-14.11964174766414</v>
+        <v>-14.92706725196469</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.78639618063787</v>
       </c>
       <c r="E8">
-        <v>-12.14196848129974</v>
+        <v>-10.82068656313374</v>
       </c>
       <c r="F8">
-        <v>1.437843580039272</v>
+        <v>1.439983166731031</v>
       </c>
       <c r="G8">
-        <v>-14.41714888836905</v>
+        <v>-14.20999150124916</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.43464680767566</v>
       </c>
       <c r="E9">
-        <v>-11.87613800010148</v>
+        <v>-10.73030727888866</v>
       </c>
       <c r="F9">
-        <v>1.582220546114394</v>
+        <v>1.942743279234607</v>
       </c>
       <c r="G9">
-        <v>-14.0223315720828</v>
+        <v>-13.31659443983928</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.1799227932923</v>
       </c>
       <c r="E10">
-        <v>-11.69628512641284</v>
+        <v>-10.91811215293476</v>
       </c>
       <c r="F10">
-        <v>1.576805855589506</v>
+        <v>1.523908494307913</v>
       </c>
       <c r="G10">
-        <v>-13.95143789463208</v>
+        <v>-12.30915239514705</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.01180684041255</v>
       </c>
       <c r="E11">
-        <v>-12.86381629507041</v>
+        <v>-12.32359198832538</v>
       </c>
       <c r="F11">
-        <v>2.027677427479624</v>
+        <v>1.740969643372128</v>
       </c>
       <c r="G11">
-        <v>-12.95455649021012</v>
+        <v>-12.7154722019095</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.90711117050248</v>
       </c>
       <c r="E12">
-        <v>-13.20643611001674</v>
+        <v>-12.59514646066934</v>
       </c>
       <c r="F12">
-        <v>1.523886322425097</v>
+        <v>1.939704147582878</v>
       </c>
       <c r="G12">
-        <v>-12.69105692855737</v>
+        <v>-11.54144681622668</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.83676779253982</v>
       </c>
       <c r="E13">
-        <v>-13.96983267280779</v>
+        <v>-12.47856089734186</v>
       </c>
       <c r="F13">
-        <v>2.185827883901323</v>
+        <v>2.128781213121278</v>
       </c>
       <c r="G13">
-        <v>-11.83032170943794</v>
+        <v>-11.86053374802933</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.77522370672372</v>
       </c>
       <c r="E14">
-        <v>-13.85470074963678</v>
+        <v>-13.5627092740962</v>
       </c>
       <c r="F14">
-        <v>2.182972462135786</v>
+        <v>1.922836095877533</v>
       </c>
       <c r="G14">
-        <v>-11.71069183583084</v>
+        <v>-11.19868286272716</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.69367443161571</v>
       </c>
       <c r="E15">
-        <v>-15.35733446638795</v>
+        <v>-14.24142790141782</v>
       </c>
       <c r="F15">
-        <v>2.706833872256677</v>
+        <v>2.163852380618685</v>
       </c>
       <c r="G15">
-        <v>-10.88589589908574</v>
+        <v>-9.591972485607132</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.57061856262675</v>
       </c>
       <c r="E16">
-        <v>-14.82971290280626</v>
+        <v>-14.32516844276766</v>
       </c>
       <c r="F16">
-        <v>2.788348799430261</v>
+        <v>2.361384852039616</v>
       </c>
       <c r="G16">
-        <v>-10.9422976634383</v>
+        <v>-9.51857438045595</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.39194927342462</v>
       </c>
       <c r="E17">
-        <v>-15.14527055708275</v>
+        <v>-15.26766162408806</v>
       </c>
       <c r="F17">
-        <v>2.988245743782943</v>
+        <v>2.282989825519449</v>
       </c>
       <c r="G17">
-        <v>-10.79964294560556</v>
+        <v>-10.11431036079334</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.15635006269043</v>
       </c>
       <c r="E18">
-        <v>-16.79476721437668</v>
+        <v>-15.76454843457969</v>
       </c>
       <c r="F18">
-        <v>3.14577855489762</v>
+        <v>2.494310040640196</v>
       </c>
       <c r="G18">
-        <v>-9.821893183855055</v>
+        <v>-9.474150169864471</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.87147822743916</v>
       </c>
       <c r="E19">
-        <v>-17.69170394717992</v>
+        <v>-17.24681760371837</v>
       </c>
       <c r="F19">
-        <v>3.772835826174461</v>
+        <v>3.485485057465297</v>
       </c>
       <c r="G19">
-        <v>-9.647745246307233</v>
+        <v>-8.459352092983977</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.54568960786107</v>
       </c>
       <c r="E20">
-        <v>-18.20388794286946</v>
+        <v>-17.29675761507496</v>
       </c>
       <c r="F20">
-        <v>3.941888514118045</v>
+        <v>3.451387869105886</v>
       </c>
       <c r="G20">
-        <v>-9.526715011937018</v>
+        <v>-8.817212134142574</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.19027665684986</v>
       </c>
       <c r="E21">
-        <v>-18.04030587629038</v>
+        <v>-19.39500340415898</v>
       </c>
       <c r="F21">
-        <v>4.030756587857015</v>
+        <v>3.745691106783829</v>
       </c>
       <c r="G21">
-        <v>-9.356605939947107</v>
+        <v>-9.378147659771145</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.81657921341925</v>
       </c>
       <c r="E22">
-        <v>-19.84054637635164</v>
+        <v>-19.10590109503529</v>
       </c>
       <c r="F22">
-        <v>4.104055248741298</v>
+        <v>3.310626503635712</v>
       </c>
       <c r="G22">
-        <v>-10.04192859312271</v>
+        <v>-7.457624049892527</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.43963730015435</v>
       </c>
       <c r="E23">
-        <v>-19.49896811042707</v>
+        <v>-19.5576707189885</v>
       </c>
       <c r="F23">
-        <v>4.300430031138044</v>
+        <v>3.619843499919349</v>
       </c>
       <c r="G23">
-        <v>-9.54265197816307</v>
+        <v>-9.214894727593066</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.07320758039967</v>
       </c>
       <c r="E24">
-        <v>-19.9083014044544</v>
+        <v>-20.21610631122977</v>
       </c>
       <c r="F24">
-        <v>4.345548228962998</v>
+        <v>3.847455297792222</v>
       </c>
       <c r="G24">
-        <v>-9.145707636367836</v>
+        <v>-7.603367506713401</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.72424701661616</v>
       </c>
       <c r="E25">
-        <v>-20.47836382643598</v>
+        <v>-20.45970651352438</v>
       </c>
       <c r="F25">
-        <v>4.140521661150207</v>
+        <v>3.811126667797956</v>
       </c>
       <c r="G25">
-        <v>-9.826200203601648</v>
+        <v>-8.152120224757454</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.39540151992333</v>
       </c>
       <c r="E26">
-        <v>-20.27674710666648</v>
+        <v>-20.31152578704539</v>
       </c>
       <c r="F26">
-        <v>4.220115553048363</v>
+        <v>3.397283723916728</v>
       </c>
       <c r="G26">
-        <v>-9.081840591824218</v>
+        <v>-7.474517763779427</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.08573442144173</v>
       </c>
       <c r="E27">
-        <v>-20.55569657706496</v>
+        <v>-19.66509517939846</v>
       </c>
       <c r="F27">
-        <v>3.976760134670107</v>
+        <v>3.512346293497066</v>
       </c>
       <c r="G27">
-        <v>-9.268416317326462</v>
+        <v>-8.486985216600274</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.7973370653208</v>
       </c>
       <c r="E28">
-        <v>-20.41155977787482</v>
+        <v>-20.15625799874439</v>
       </c>
       <c r="F28">
-        <v>3.992689048767597</v>
+        <v>3.443950786126982</v>
       </c>
       <c r="G28">
-        <v>-8.91866711273908</v>
+        <v>-7.524126288685406</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.53214096360094</v>
       </c>
       <c r="E29">
-        <v>-21.09217583580566</v>
+        <v>-20.47956840052202</v>
       </c>
       <c r="F29">
-        <v>4.079531562640718</v>
+        <v>3.374842611094951</v>
       </c>
       <c r="G29">
-        <v>-9.011564331116569</v>
+        <v>-7.324728820309563</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.29062809289995</v>
       </c>
       <c r="E30">
-        <v>-20.70274971351605</v>
+        <v>-21.07202412647153</v>
       </c>
       <c r="F30">
-        <v>4.196055892781007</v>
+        <v>3.304844393338443</v>
       </c>
       <c r="G30">
-        <v>-8.424051745898728</v>
+        <v>-7.231222461552848</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.07310521822734</v>
       </c>
       <c r="E31">
-        <v>-20.23294317759028</v>
+        <v>-20.07452809985396</v>
       </c>
       <c r="F31">
-        <v>4.014583783048547</v>
+        <v>3.267899701743072</v>
       </c>
       <c r="G31">
-        <v>-8.2635598087004</v>
+        <v>-7.827696693545495</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.879113455731391</v>
       </c>
       <c r="E32">
-        <v>-20.10780332686232</v>
+        <v>-18.91672862183887</v>
       </c>
       <c r="F32">
-        <v>4.051894310710384</v>
+        <v>3.179012623533117</v>
       </c>
       <c r="G32">
-        <v>-8.866890180504878</v>
+        <v>-7.052403344249115</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.711452106393811</v>
       </c>
       <c r="E33">
-        <v>-20.36211337018507</v>
+        <v>-19.16486635508917</v>
       </c>
       <c r="F33">
-        <v>3.735628239397127</v>
+        <v>3.215171796994431</v>
       </c>
       <c r="G33">
-        <v>-8.020261195928283</v>
+        <v>-6.897403602100439</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.569516994701598</v>
       </c>
       <c r="E34">
-        <v>-20.62668946408321</v>
+        <v>-20.11315598313939</v>
       </c>
       <c r="F34">
-        <v>3.85707156011077</v>
+        <v>3.339236150998126</v>
       </c>
       <c r="G34">
-        <v>-7.432367897973426</v>
+        <v>-6.804416998993389</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.450033963899269</v>
       </c>
       <c r="E35">
-        <v>-19.34344672758165</v>
+        <v>-19.40402412438225</v>
       </c>
       <c r="F35">
-        <v>3.625383303211556</v>
+        <v>2.941591351220012</v>
       </c>
       <c r="G35">
-        <v>-7.829755852870922</v>
+        <v>-5.954884665978853</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.346995925628196</v>
       </c>
       <c r="E36">
-        <v>-18.8077010816302</v>
+        <v>-19.90707871647233</v>
       </c>
       <c r="F36">
-        <v>3.806158582341223</v>
+        <v>3.074174459342857</v>
       </c>
       <c r="G36">
-        <v>-7.361042194329829</v>
+        <v>-6.040372883439453</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.254301518220357</v>
       </c>
       <c r="E37">
-        <v>-18.48892368233425</v>
+        <v>-19.32398787477069</v>
       </c>
       <c r="F37">
-        <v>3.697793505077279</v>
+        <v>3.296878352583783</v>
       </c>
       <c r="G37">
-        <v>-7.590688117297993</v>
+        <v>-5.934680406552681</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.170649919014011</v>
       </c>
       <c r="E38">
-        <v>-19.32315010707927</v>
+        <v>-18.26992215084931</v>
       </c>
       <c r="F38">
-        <v>3.950516543945359</v>
+        <v>3.153480116764402</v>
       </c>
       <c r="G38">
-        <v>-7.009816486431931</v>
+        <v>-6.685277086126098</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.092279273343586</v>
       </c>
       <c r="E39">
-        <v>-19.09996879408525</v>
+        <v>-17.75335459232034</v>
       </c>
       <c r="F39">
-        <v>4.140013291551351</v>
+        <v>3.217824504402792</v>
       </c>
       <c r="G39">
-        <v>-6.697344024616741</v>
+        <v>-5.439164571325648</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.015836707068457</v>
       </c>
       <c r="E40">
-        <v>-19.11054278089316</v>
+        <v>-17.75621658789319</v>
       </c>
       <c r="F40">
-        <v>3.816159685197223</v>
+        <v>3.303821319317069</v>
       </c>
       <c r="G40">
-        <v>-6.826832702839795</v>
+        <v>-6.234725080413447</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.937100905460621</v>
       </c>
       <c r="E41">
-        <v>-19.70787567334892</v>
+        <v>-18.15661973117739</v>
       </c>
       <c r="F41">
-        <v>3.736876199658493</v>
+        <v>3.567802923538009</v>
       </c>
       <c r="G41">
-        <v>-6.93937138790178</v>
+        <v>-5.70770278328917</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.853808500470741</v>
       </c>
       <c r="E42">
-        <v>-18.46025391339169</v>
+        <v>-18.43936859126832</v>
       </c>
       <c r="F42">
-        <v>3.90882073460367</v>
+        <v>3.683633590487335</v>
       </c>
       <c r="G42">
-        <v>-7.126109330135449</v>
+        <v>-6.126447067460504</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.766619302101388</v>
       </c>
       <c r="E43">
-        <v>-17.50252241703548</v>
+        <v>-17.87287460680479</v>
       </c>
       <c r="F43">
-        <v>3.701957067928969</v>
+        <v>3.58613115209739</v>
       </c>
       <c r="G43">
-        <v>-7.25670042002308</v>
+        <v>-6.123911189577422</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.675280850546086</v>
       </c>
       <c r="E44">
-        <v>-17.94335577626017</v>
+        <v>-16.29542597097289</v>
       </c>
       <c r="F44">
-        <v>3.999196496374137</v>
+        <v>3.323527372022882</v>
       </c>
       <c r="G44">
-        <v>-7.272703597159916</v>
+        <v>-6.630202850534783</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.580271127930732</v>
       </c>
       <c r="E45">
-        <v>-18.40072712256087</v>
+        <v>-16.83304187668951</v>
       </c>
       <c r="F45">
-        <v>3.62231566485335</v>
+        <v>3.570248165471448</v>
       </c>
       <c r="G45">
-        <v>-7.075193139741458</v>
+        <v>-7.109043467880506</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.480559602850375</v>
       </c>
       <c r="E46">
-        <v>-18.02860429945456</v>
+        <v>-17.18771648944426</v>
       </c>
       <c r="F46">
-        <v>3.602441739320501</v>
+        <v>3.671475480174506</v>
       </c>
       <c r="G46">
-        <v>-7.690239532209416</v>
+        <v>-6.716637884019613</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.379052076983385</v>
       </c>
       <c r="E47">
-        <v>-18.30010443011043</v>
+        <v>-17.19828141930416</v>
       </c>
       <c r="F47">
-        <v>3.63891131914124</v>
+        <v>3.284414587029274</v>
       </c>
       <c r="G47">
-        <v>-7.439270385422807</v>
+        <v>-7.596683515269612</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.280870525467904</v>
       </c>
       <c r="E48">
-        <v>-17.5143417341955</v>
+        <v>-17.1973077973925</v>
       </c>
       <c r="F48">
-        <v>3.677539490124724</v>
+        <v>3.221094857118174</v>
       </c>
       <c r="G48">
-        <v>-8.29503978623333</v>
+        <v>-7.700283727375565</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.187688438233675</v>
       </c>
       <c r="E49">
-        <v>-17.18032149138973</v>
+        <v>-16.84314943067463</v>
       </c>
       <c r="F49">
-        <v>3.519449214527812</v>
+        <v>3.17186852614857</v>
       </c>
       <c r="G49">
-        <v>-8.13973547389504</v>
+        <v>-8.035810828326239</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.097057712722295</v>
       </c>
       <c r="E50">
-        <v>-17.18504468977973</v>
+        <v>-16.1976064039332</v>
       </c>
       <c r="F50">
-        <v>3.786495289695126</v>
+        <v>3.376515004541655</v>
       </c>
       <c r="G50">
-        <v>-8.02349890946569</v>
+        <v>-8.096185247325927</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.007731965949656</v>
       </c>
       <c r="E51">
-        <v>-16.0811204670339</v>
+        <v>-16.27244396538396</v>
       </c>
       <c r="F51">
-        <v>3.728495227953988</v>
+        <v>3.086992975022424</v>
       </c>
       <c r="G51">
-        <v>-8.917624290894208</v>
+        <v>-7.338229225018711</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.925780053559981</v>
       </c>
       <c r="E52">
-        <v>-17.1661926524858</v>
+        <v>-14.67931775253752</v>
       </c>
       <c r="F52">
-        <v>3.644015603306701</v>
+        <v>3.193712581840226</v>
       </c>
       <c r="G52">
-        <v>-7.698704597153333</v>
+        <v>-7.828077406282511</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.858128816636174</v>
       </c>
       <c r="E53">
-        <v>-17.21323444047748</v>
+        <v>-14.98684642239841</v>
       </c>
       <c r="F53">
-        <v>3.328707674072285</v>
+        <v>3.386739409931732</v>
       </c>
       <c r="G53">
-        <v>-8.598825376553473</v>
+        <v>-8.124910850970185</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.812341076896162</v>
       </c>
       <c r="E54">
-        <v>-16.70451925587782</v>
+        <v>-15.20640948466031</v>
       </c>
       <c r="F54">
-        <v>3.404316961887195</v>
+        <v>3.171534364200412</v>
       </c>
       <c r="G54">
-        <v>-9.117399161461529</v>
+        <v>-8.769844848566683</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.793839162688926</v>
       </c>
       <c r="E55">
-        <v>-16.58579625281872</v>
+        <v>-14.5137612712911</v>
       </c>
       <c r="F55">
-        <v>3.322852713302905</v>
+        <v>3.221994402078144</v>
       </c>
       <c r="G55">
-        <v>-8.214676293267523</v>
+        <v>-7.962147879531916</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.804668005654386</v>
       </c>
       <c r="E56">
-        <v>-16.54811934907491</v>
+        <v>-14.80164994938072</v>
       </c>
       <c r="F56">
-        <v>3.315154318847954</v>
+        <v>3.17037509147031</v>
       </c>
       <c r="G56">
-        <v>-8.593452361143235</v>
+        <v>-8.239131293166119</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.847377109492029</v>
       </c>
       <c r="E57">
-        <v>-16.12349792679768</v>
+        <v>-15.13767630617189</v>
       </c>
       <c r="F57">
-        <v>3.26803906786363</v>
+        <v>2.793497427361354</v>
       </c>
       <c r="G57">
-        <v>-8.898780665684678</v>
+        <v>-7.867916511302101</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.921383201620044</v>
       </c>
       <c r="E58">
-        <v>-16.24280510300376</v>
+        <v>-15.87745234853893</v>
       </c>
       <c r="F58">
-        <v>3.176920548018822</v>
+        <v>2.905855027238121</v>
       </c>
       <c r="G58">
-        <v>-8.430378198424275</v>
+        <v>-8.579776497520506</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.024985622468392</v>
       </c>
       <c r="E59">
-        <v>-16.02198765344174</v>
+        <v>-14.48151400788248</v>
       </c>
       <c r="F59">
-        <v>3.419878456212303</v>
+        <v>2.647449651545444</v>
       </c>
       <c r="G59">
-        <v>-8.552385043728576</v>
+        <v>-8.562654355991395</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.155318641438749</v>
       </c>
       <c r="E60">
-        <v>-16.14840906231387</v>
+        <v>-14.2623766221773</v>
       </c>
       <c r="F60">
-        <v>3.137446678076493</v>
+        <v>3.100167824532964</v>
       </c>
       <c r="G60">
-        <v>-8.955294988585576</v>
+        <v>-8.120385335218</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.309690486217731</v>
       </c>
       <c r="E61">
-        <v>-16.62854504745113</v>
+        <v>-15.00850158510309</v>
       </c>
       <c r="F61">
-        <v>3.275121400717476</v>
+        <v>2.675516087778862</v>
       </c>
       <c r="G61">
-        <v>-9.096963163847608</v>
+        <v>-7.886220517588732</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.485777888027231</v>
       </c>
       <c r="E62">
-        <v>-16.27335871713352</v>
+        <v>-14.62066495719017</v>
       </c>
       <c r="F62">
-        <v>3.428767797515664</v>
+        <v>3.010785046371477</v>
       </c>
       <c r="G62">
-        <v>-9.447871059373735</v>
+        <v>-8.0139148801295</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.67620672485428</v>
       </c>
       <c r="E63">
-        <v>-15.64145092562918</v>
+        <v>-14.18272529285639</v>
       </c>
       <c r="F63">
-        <v>2.986690544573982</v>
+        <v>2.817910254047853</v>
       </c>
       <c r="G63">
-        <v>-8.915869701758396</v>
+        <v>-9.43749580965366</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.871904059120881</v>
       </c>
       <c r="E64">
-        <v>-15.97584250330358</v>
+        <v>-13.90049720727635</v>
       </c>
       <c r="F64">
-        <v>3.099942938292972</v>
+        <v>3.072920164257829</v>
       </c>
       <c r="G64">
-        <v>-9.398030796280008</v>
+        <v>-9.321884938331232</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.062538279205953</v>
       </c>
       <c r="E65">
-        <v>-15.34530683942357</v>
+        <v>-13.34737580655747</v>
       </c>
       <c r="F65">
-        <v>3.619712052328368</v>
+        <v>2.840919917293273</v>
       </c>
       <c r="G65">
-        <v>-9.649691847084325</v>
+        <v>-9.272418766883442</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.242088013269615</v>
       </c>
       <c r="E66">
-        <v>-16.75511136749151</v>
+        <v>-13.90036588153012</v>
       </c>
       <c r="F66">
-        <v>3.224930592845368</v>
+        <v>3.052229046472612</v>
       </c>
       <c r="G66">
-        <v>-9.882360298129843</v>
+        <v>-8.497989469972811</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.408864734945396</v>
       </c>
       <c r="E67">
-        <v>-15.86357710417942</v>
+        <v>-14.57407148812525</v>
       </c>
       <c r="F67">
-        <v>3.325278950765358</v>
+        <v>2.776041820761381</v>
       </c>
       <c r="G67">
-        <v>-9.03467524952622</v>
+        <v>-8.924490362342658</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.561024154704278</v>
       </c>
       <c r="E68">
-        <v>-16.00192198511375</v>
+        <v>-13.08676212741604</v>
       </c>
       <c r="F68">
-        <v>3.142474944358014</v>
+        <v>2.866001067876088</v>
       </c>
       <c r="G68">
-        <v>-9.463400828498457</v>
+        <v>-9.182709603860271</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.69743574617365</v>
       </c>
       <c r="E69">
-        <v>-16.13580179067652</v>
+        <v>-14.96468407060487</v>
       </c>
       <c r="F69">
-        <v>3.130899637822067</v>
+        <v>2.611128940080755</v>
       </c>
       <c r="G69">
-        <v>-10.28095991269471</v>
+        <v>-9.64435855822056</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.81488096298467</v>
       </c>
       <c r="E70">
-        <v>-15.64434914899409</v>
+        <v>-14.16602880919011</v>
       </c>
       <c r="F70">
-        <v>3.103249716244409</v>
+        <v>2.86718092878309</v>
       </c>
       <c r="G70">
-        <v>-9.55836713783799</v>
+        <v>-9.513115290861693</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.913971120953377</v>
       </c>
       <c r="E71">
-        <v>-16.25158128563063</v>
+        <v>-13.68151831816144</v>
       </c>
       <c r="F71">
-        <v>3.058391246189587</v>
+        <v>2.748295293122882</v>
       </c>
       <c r="G71">
-        <v>-10.21404385570942</v>
+        <v>-9.457465020346543</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.996085250520645</v>
       </c>
       <c r="E72">
-        <v>-16.5404390571579</v>
+        <v>-15.00312628645599</v>
       </c>
       <c r="F72">
-        <v>3.023077771687118</v>
+        <v>3.044636760313995</v>
       </c>
       <c r="G72">
-        <v>-10.22462104870739</v>
+        <v>-9.274557379301811</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.06225156021513</v>
       </c>
       <c r="E73">
-        <v>-15.85039018786909</v>
+        <v>-14.46448694561364</v>
       </c>
       <c r="F73">
-        <v>3.316478296993261</v>
+        <v>2.745138967233411</v>
       </c>
       <c r="G73">
-        <v>-10.36331304352962</v>
+        <v>-10.02930217243593</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.11275673046875</v>
       </c>
       <c r="E74">
-        <v>-16.22386702470369</v>
+        <v>-14.50238121610982</v>
       </c>
       <c r="F74">
-        <v>2.933785264762812</v>
+        <v>2.846485059880127</v>
       </c>
       <c r="G74">
-        <v>-10.2157189917523</v>
+        <v>-9.770549933086498</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.14628687900165</v>
       </c>
       <c r="E75">
-        <v>-17.57658108095692</v>
+        <v>-15.15988847117951</v>
       </c>
       <c r="F75">
-        <v>3.104104917438747</v>
+        <v>2.542084113285342</v>
       </c>
       <c r="G75">
-        <v>-10.67300133654629</v>
+        <v>-10.27798373225491</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.16463015061721</v>
       </c>
       <c r="E76">
-        <v>-17.35158384988582</v>
+        <v>-14.57015888658262</v>
       </c>
       <c r="F76">
-        <v>2.936072136104706</v>
+        <v>2.52625655636644</v>
       </c>
       <c r="G76">
-        <v>-10.61742058748746</v>
+        <v>-8.921812131001387</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.16874814017445</v>
       </c>
       <c r="E77">
-        <v>-17.39008493589903</v>
+        <v>-15.99797768425307</v>
       </c>
       <c r="F77">
-        <v>2.82254734496826</v>
+        <v>2.56413246704009</v>
       </c>
       <c r="G77">
-        <v>-10.82693177248578</v>
+        <v>-10.02749792511703</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.15778230928045</v>
       </c>
       <c r="E78">
-        <v>-18.07816391899451</v>
+        <v>-15.62480425517699</v>
       </c>
       <c r="F78">
-        <v>2.77272554057445</v>
+        <v>2.3955818138717</v>
       </c>
       <c r="G78">
-        <v>-10.54878635736729</v>
+        <v>-10.76198217955081</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.12855672077537</v>
       </c>
       <c r="E79">
-        <v>-18.41262795225302</v>
+        <v>-16.0447522922783</v>
       </c>
       <c r="F79">
-        <v>2.966902139160565</v>
+        <v>2.85092893867885</v>
       </c>
       <c r="G79">
-        <v>-10.50038287103761</v>
+        <v>-9.966418359917478</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.07613621418092</v>
       </c>
       <c r="E80">
-        <v>-19.53336639898934</v>
+        <v>-16.05711502631924</v>
       </c>
       <c r="F80">
-        <v>2.805178842193635</v>
+        <v>2.216833678313797</v>
       </c>
       <c r="G80">
-        <v>-11.03058329187958</v>
+        <v>-9.920646757291514</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.997802650766205</v>
       </c>
       <c r="E81">
-        <v>-18.97058123473809</v>
+        <v>-16.53374597257456</v>
       </c>
       <c r="F81">
-        <v>2.611428260498774</v>
+        <v>2.016982661432662</v>
       </c>
       <c r="G81">
-        <v>-11.61489126901541</v>
+        <v>-10.88766373040371</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.890364930506125</v>
       </c>
       <c r="E82">
-        <v>-20.26917549812566</v>
+        <v>-17.3147311284114</v>
       </c>
       <c r="F82">
-        <v>2.563256677668852</v>
+        <v>2.291617855346762</v>
       </c>
       <c r="G82">
-        <v>-10.7254205146151</v>
+        <v>-10.13753714829687</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.750539170633076</v>
       </c>
       <c r="E83">
-        <v>-20.58401312503493</v>
+        <v>-17.62720036341466</v>
       </c>
       <c r="F83">
-        <v>2.610737764719642</v>
+        <v>2.172038556495592</v>
       </c>
       <c r="G83">
-        <v>-11.07319332351554</v>
+        <v>-9.530058662931681</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.574974496527195</v>
       </c>
       <c r="E84">
-        <v>-20.55029863604782</v>
+        <v>-19.24964391698677</v>
       </c>
       <c r="F84">
-        <v>2.934876438138549</v>
+        <v>2.336888088939599</v>
       </c>
       <c r="G84">
-        <v>-11.06239432396644</v>
+        <v>-10.50854005524637</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.360623953344676</v>
       </c>
       <c r="E85">
-        <v>-21.65134274932478</v>
+        <v>-19.334208640606</v>
       </c>
       <c r="F85">
-        <v>2.401376593816293</v>
+        <v>2.09790211518204</v>
       </c>
       <c r="G85">
-        <v>-10.82951730855195</v>
+        <v>-10.52825104338719</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.110865808005157</v>
       </c>
       <c r="E86">
-        <v>-22.83771689832826</v>
+        <v>-20.72053755941817</v>
       </c>
       <c r="F86">
-        <v>2.518844812682183</v>
+        <v>2.481491524960629</v>
       </c>
       <c r="G86">
-        <v>-10.77703191957234</v>
+        <v>-10.0797780602732</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.832476384158232</v>
       </c>
       <c r="E87">
-        <v>-24.91534907372937</v>
+        <v>-20.93582121374282</v>
       </c>
       <c r="F87">
-        <v>2.619761721025816</v>
+        <v>1.927064590671756</v>
       </c>
       <c r="G87">
-        <v>-11.43603904625628</v>
+        <v>-10.05463777744798</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.534336992907194</v>
       </c>
       <c r="E88">
-        <v>-25.62038266350956</v>
+        <v>-22.99607310590249</v>
       </c>
       <c r="F88">
-        <v>2.700666921421956</v>
+        <v>2.588163620600968</v>
       </c>
       <c r="G88">
-        <v>-11.12846950238475</v>
+        <v>-9.293887654705616</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.223318636806217</v>
       </c>
       <c r="E89">
-        <v>-26.87638662885499</v>
+        <v>-26.0158452416514</v>
       </c>
       <c r="F89">
-        <v>2.718266645260234</v>
+        <v>2.076346293966994</v>
       </c>
       <c r="G89">
-        <v>-10.91210879866568</v>
+        <v>-9.28295954388048</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.904108057836443</v>
       </c>
       <c r="E90">
-        <v>-27.91308112648295</v>
+        <v>-25.99520445712444</v>
       </c>
       <c r="F90">
-        <v>2.638066193996465</v>
+        <v>2.137413994066339</v>
       </c>
       <c r="G90">
-        <v>-10.34735952457588</v>
+        <v>-9.365584139449611</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.58319241440772</v>
       </c>
       <c r="E91">
-        <v>-28.98809104268981</v>
+        <v>-28.11879611522939</v>
       </c>
       <c r="F91">
-        <v>2.68102421695276</v>
+        <v>2.263942594474458</v>
       </c>
       <c r="G91">
-        <v>-10.81918840646942</v>
+        <v>-9.420386910306707</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.262434323361511</v>
       </c>
       <c r="E92">
-        <v>-31.52995746675024</v>
+        <v>-29.34626616585249</v>
       </c>
       <c r="F92">
-        <v>2.449193426521157</v>
+        <v>2.153433179401009</v>
       </c>
       <c r="G92">
-        <v>-10.05194299337901</v>
+        <v>-8.83117601522722</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.942027336340489</v>
       </c>
       <c r="E93">
-        <v>-33.48782735430749</v>
+        <v>-31.8238871291661</v>
       </c>
       <c r="F93">
-        <v>2.823291686748516</v>
+        <v>2.217817159687284</v>
       </c>
       <c r="G93">
-        <v>-10.23554253844145</v>
+        <v>-8.277712390880785</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.620086230646333</v>
       </c>
       <c r="E94">
-        <v>-35.49670144461313</v>
+        <v>-33.54194488293615</v>
       </c>
       <c r="F94">
-        <v>2.679209289973667</v>
+        <v>2.067384102191522</v>
       </c>
       <c r="G94">
-        <v>-9.309503498014358</v>
+        <v>-8.311423676107184</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.295788267408962</v>
       </c>
       <c r="E95">
-        <v>-37.51826205485126</v>
+        <v>-37.5785632147374</v>
       </c>
       <c r="F95">
-        <v>2.681238017251344</v>
+        <v>2.348610680125682</v>
       </c>
       <c r="G95">
-        <v>-9.792409465282306</v>
+        <v>-8.391333624334111</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.970745151834874</v>
       </c>
       <c r="E96">
-        <v>-40.0610160598172</v>
+        <v>-38.41130430000791</v>
       </c>
       <c r="F96">
-        <v>3.034542218808984</v>
+        <v>2.72996389715167</v>
       </c>
       <c r="G96">
-        <v>-9.165243165595076</v>
+        <v>-7.508722320291177</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.64850196325663</v>
       </c>
       <c r="E97">
-        <v>-42.69474937183423</v>
+        <v>-41.28811251133466</v>
       </c>
       <c r="F97">
-        <v>2.671160896511403</v>
+        <v>2.343660015434018</v>
       </c>
       <c r="G97">
-        <v>-8.779471914994883</v>
+        <v>-7.297300950516702</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.331531361700439</v>
       </c>
       <c r="E98">
-        <v>-44.22898051597392</v>
+        <v>-42.64474369760453</v>
       </c>
       <c r="F98">
-        <v>2.705904236884314</v>
+        <v>2.916331241868753</v>
       </c>
       <c r="G98">
-        <v>-9.259745998559112</v>
+        <v>-8.130806932575625</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.026461663269695</v>
       </c>
       <c r="E99">
-        <v>-46.6424103602288</v>
+        <v>-45.70277917448125</v>
       </c>
       <c r="F99">
-        <v>2.735072932434877</v>
+        <v>2.484115725662512</v>
       </c>
       <c r="G99">
-        <v>-8.829742549008715</v>
+        <v>-7.914767351773867</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.734286594859743</v>
       </c>
       <c r="E100">
-        <v>-49.47259113893558</v>
+        <v>-47.84185368521842</v>
       </c>
       <c r="F100">
-        <v>2.605565381199817</v>
+        <v>2.619961267971161</v>
       </c>
       <c r="G100">
-        <v>-9.037783851787596</v>
+        <v>-8.056462011400212</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.466855851718684</v>
       </c>
       <c r="E101">
-        <v>-50.5978795699311</v>
+        <v>-50.13930364954436</v>
       </c>
       <c r="F101">
-        <v>2.601751817355439</v>
+        <v>2.173226335932171</v>
       </c>
       <c r="G101">
-        <v>-10.03967742215601</v>
+        <v>-8.161121598078733</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.216245142823634</v>
       </c>
       <c r="E102">
-        <v>-53.11612773780453</v>
+        <v>-52.79256260936397</v>
       </c>
       <c r="F102">
-        <v>3.21938762214133</v>
+        <v>2.453263550723836</v>
       </c>
       <c r="G102">
-        <v>-9.246252214941041</v>
+        <v>-8.135719782155904</v>
       </c>
     </row>
   </sheetData>
